--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6133439</v>
+        <v>135288243</v>
       </c>
       <c r="B13" t="n">
-        <v>107516</v>
+        <v>109896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1899,17 +1899,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601196</v>
+        <v>601301</v>
       </c>
       <c r="R13" t="n">
-        <v>6276957</v>
+        <v>6276866</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,17 +1933,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4H5a NV</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,73 +1954,65 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>torräng</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16071739</v>
+        <v>6133439</v>
       </c>
       <c r="B14" t="n">
-        <v>101325</v>
+        <v>107516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601122</v>
+        <v>601196</v>
       </c>
       <c r="R14" t="n">
-        <v>6276910</v>
+        <v>6276957</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2047,12 +2039,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,18 +2063,18 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>torräng</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2088,32 +2085,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>60128607</v>
+        <v>16071739</v>
       </c>
       <c r="B15" t="n">
-        <v>100797</v>
+        <v>101325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222617</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601191</v>
+        <v>601122</v>
       </c>
       <c r="R15" t="n">
-        <v>6276883</v>
+        <v>6276910</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,12 +2153,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,18 +2172,18 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grusgrop, f d banvall</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2197,32 +2194,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54593753</v>
+        <v>60128607</v>
       </c>
       <c r="B16" t="n">
-        <v>106230</v>
+        <v>100797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224098</v>
+        <v>222617</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601121</v>
+        <v>601191</v>
       </c>
       <c r="R16" t="n">
-        <v>6276914</v>
+        <v>6276883</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2265,12 +2262,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,16 +2278,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grusgrop, f d banvall</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2301,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6250674</v>
+        <v>135288104</v>
       </c>
       <c r="B17" t="n">
-        <v>104640</v>
+        <v>100875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,38 +2314,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224416</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601191</v>
+        <v>601301</v>
       </c>
       <c r="R17" t="n">
-        <v>6276888</v>
+        <v>6276866</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2367,12 +2368,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,70 +2384,68 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>f.d. banvall, kalkrik sand</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72696194</v>
+        <v>54593753</v>
       </c>
       <c r="B18" t="n">
-        <v>104640</v>
+        <v>106230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>224098</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601208</v>
+        <v>601121</v>
       </c>
       <c r="R18" t="n">
-        <v>6276952</v>
+        <v>6276914</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2473,12 +2472,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,27 +2486,235 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>torräng vid gammal skjutbana</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6250674</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>601191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6276888</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2009-10-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2009-10-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>f.d. banvall, kalkrik sand</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>72696194</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dörbyskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>601208</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6276952</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>torräng vid gammal skjutbana</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,51 +1428,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61030053</v>
+        <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>100693</v>
+        <v>104760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Väg 925, fyndplats 020, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601191</v>
+        <v>601307</v>
       </c>
       <c r="R9" t="n">
-        <v>6276883</v>
+        <v>6276876</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,14 +1491,20 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,65 +1519,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72696177</v>
+        <v>61030053</v>
       </c>
       <c r="B10" t="n">
-        <v>111175</v>
+        <v>100693</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>1888</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601200</v>
+        <v>601191</v>
       </c>
       <c r="R10" t="n">
-        <v>6276869</v>
+        <v>6276883</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,17 +1603,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>groddplantor</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,24 +1617,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gammalt sandtag</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1648,45 +1639,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2671390</v>
+        <v>72696177</v>
       </c>
       <c r="B11" t="n">
-        <v>104639</v>
+        <v>111175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220164</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601196</v>
+        <v>601200</v>
       </c>
       <c r="R11" t="n">
-        <v>6276957</v>
+        <v>6276869</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1713,17 +1708,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>4H5a NV</t>
+          <t>groddplantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,23 +1727,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>torräng</t>
+          <t>gammalt sandtag</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1759,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60128602</v>
+        <v>2671390</v>
       </c>
       <c r="B12" t="n">
-        <v>109814</v>
+        <v>104639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,37 +1766,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220204</v>
+        <v>220164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601191</v>
+        <v>601196</v>
       </c>
       <c r="R12" t="n">
-        <v>6276883</v>
+        <v>6276957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1827,12 +1820,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,18 +1844,18 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grusgrop, f d banvall</t>
+          <t>torräng</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1868,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135288243</v>
+        <v>60128602</v>
       </c>
       <c r="B13" t="n">
-        <v>109896</v>
+        <v>109814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,19 +1895,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601301</v>
+        <v>601191</v>
       </c>
       <c r="R13" t="n">
-        <v>6276866</v>
+        <v>6276883</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,17 +1934,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,30 +1950,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grusgrop, f d banvall</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6133439</v>
+        <v>135288243</v>
       </c>
       <c r="B14" t="n">
-        <v>107516</v>
+        <v>109896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,16 +1986,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2005,17 +2006,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601196</v>
+        <v>601301</v>
       </c>
       <c r="R14" t="n">
-        <v>6276957</v>
+        <v>6276866</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,17 +2040,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4H5a NV</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,73 +2061,65 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>torräng</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16071739</v>
+        <v>6133439</v>
       </c>
       <c r="B15" t="n">
-        <v>101325</v>
+        <v>107516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601122</v>
+        <v>601196</v>
       </c>
       <c r="R15" t="n">
-        <v>6276910</v>
+        <v>6276957</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2153,12 +2146,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,18 +2170,18 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>torräng</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2194,32 +2192,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60128607</v>
+        <v>16071739</v>
       </c>
       <c r="B16" t="n">
-        <v>100797</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222617</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2232,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601191</v>
+        <v>601122</v>
       </c>
       <c r="R16" t="n">
-        <v>6276883</v>
+        <v>6276910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2262,12 +2260,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,18 +2279,18 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grusgrop, f d banvall</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2303,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135288104</v>
+        <v>60128607</v>
       </c>
       <c r="B17" t="n">
-        <v>100875</v>
+        <v>100797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,19 +2330,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601301</v>
+        <v>601191</v>
       </c>
       <c r="R17" t="n">
-        <v>6276866</v>
+        <v>6276883</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2368,12 +2369,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,71 +2385,73 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grusgrop, f d banvall</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54593753</v>
+        <v>135288104</v>
       </c>
       <c r="B18" t="n">
-        <v>106230</v>
+        <v>100875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224098</v>
+        <v>222617</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601121</v>
+        <v>601301</v>
       </c>
       <c r="R18" t="n">
-        <v>6276914</v>
+        <v>6276866</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,12 +2475,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,62 +2495,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6250674</v>
+        <v>54593753</v>
       </c>
       <c r="B19" t="n">
-        <v>104640</v>
+        <v>106230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224416</v>
+        <v>224098</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601191</v>
+        <v>601121</v>
       </c>
       <c r="R19" t="n">
-        <v>6276888</v>
+        <v>6276914</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2574,12 +2579,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,11 +2595,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>f.d. banvall, kalkrik sand</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>72696194</v>
+        <v>6250674</v>
       </c>
       <c r="B20" t="n">
         <v>104640</v>
@@ -2640,20 +2640,21 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601208</v>
+        <v>601191</v>
       </c>
       <c r="R20" t="n">
-        <v>6276952</v>
+        <v>6276888</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2680,12 +2681,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,27 +2695,133 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>torräng vid gammal skjutbana</t>
+          <t>f.d. banvall, kalkrik sand</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>72696194</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dörbyskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>601208</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6276952</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>torräng vid gammal skjutbana</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86569798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113030917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113055470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113123273</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113215087</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/471871</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135447260</t>
         </is>
       </c>
     </row>
@@ -1634,6 +1679,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61030053</t>
         </is>
       </c>
     </row>
@@ -1752,6 +1802,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72696177</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2671390</t>
         </is>
       </c>
     </row>
@@ -1972,6 +2032,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60128602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135288243</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2187,6 +2257,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6133439</t>
         </is>
       </c>
     </row>
@@ -2298,6 +2373,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071739</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2407,6 +2487,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60128607</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135288104</t>
         </is>
       </c>
     </row>
@@ -2612,6 +2702,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54593753</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2717,6 +2812,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6250674</t>
         </is>
       </c>
     </row>
@@ -2826,8 +2926,35 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72696194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>104760</v>
+        <v>104814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>135288243</v>
       </c>
       <c r="B14" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135288104</v>
       </c>
       <c r="B18" t="n">
-        <v>100875</v>
+        <v>100923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>104814</v>
+        <v>104841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>135288243</v>
       </c>
       <c r="B14" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135288104</v>
       </c>
       <c r="B18" t="n">
-        <v>100923</v>
+        <v>100950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,51 +1468,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61030053</v>
+        <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>100693</v>
+        <v>104846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Väg 925, fyndplats 020, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601191</v>
+        <v>601307</v>
       </c>
       <c r="R9" t="n">
-        <v>6276883</v>
+        <v>6276876</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,14 +1531,20 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,70 +1559,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61030053</t>
+          <t>https://artportalen.se/Sighting/135447260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72696177</v>
+        <v>61030053</v>
       </c>
       <c r="B10" t="n">
-        <v>111175</v>
+        <v>100693</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>1888</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601200</v>
+        <v>601191</v>
       </c>
       <c r="R10" t="n">
-        <v>6276869</v>
+        <v>6276883</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,17 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>groddplantor</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,24 +1662,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gammalt sandtag</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1692,51 +1683,55 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696177</t>
+          <t>https://artportalen.se/Sighting/61030053</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2671390</v>
+        <v>72696177</v>
       </c>
       <c r="B11" t="n">
-        <v>104639</v>
+        <v>111175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220164</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601196</v>
+        <v>601200</v>
       </c>
       <c r="R11" t="n">
-        <v>6276957</v>
+        <v>6276869</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,17 +1758,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>4H5a NV</t>
+          <t>groddplantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,23 +1777,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>torräng</t>
+          <t>gammalt sandtag</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1808,16 +1804,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2671390</t>
+          <t>https://artportalen.se/Sighting/72696177</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60128602</v>
+        <v>2671390</v>
       </c>
       <c r="B12" t="n">
-        <v>109814</v>
+        <v>104639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,37 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220204</v>
+        <v>220164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601191</v>
+        <v>601196</v>
       </c>
       <c r="R12" t="n">
-        <v>6276883</v>
+        <v>6276957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1882,12 +1875,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,18 +1899,18 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grusgrop, f d banvall</t>
+          <t>torräng</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1922,16 +1920,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60128602</t>
+          <t>https://artportalen.se/Sighting/2671390</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6133439</v>
+        <v>60128602</v>
       </c>
       <c r="B13" t="n">
-        <v>107516</v>
+        <v>109814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,16 +1937,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1957,16 +1955,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601196</v>
+        <v>601191</v>
       </c>
       <c r="R13" t="n">
-        <v>6276957</v>
+        <v>6276883</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,17 +1994,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,18 +2013,18 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>torräng</t>
+          <t>Grusgrop, f d banvall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2038,57 +2034,54 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6133439</t>
+          <t>https://artportalen.se/Sighting/60128602</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16071739</v>
+        <v>135288243</v>
       </c>
       <c r="B14" t="n">
-        <v>101325</v>
+        <v>109984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601122</v>
+        <v>601301</v>
       </c>
       <c r="R14" t="n">
-        <v>6276910</v>
+        <v>6276866</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,12 +2105,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,40 +2126,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071739</t>
+          <t>https://artportalen.se/Sighting/135288243</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>60128607</v>
+        <v>6133439</v>
       </c>
       <c r="B15" t="n">
-        <v>100797</v>
+        <v>107516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,37 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601191</v>
+        <v>601196</v>
       </c>
       <c r="R15" t="n">
-        <v>6276883</v>
+        <v>6276957</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,12 +2216,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,18 +2240,18 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grusgrop, f d banvall</t>
+          <t>torräng</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2266,16 +2261,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60128607</t>
+          <t>https://artportalen.se/Sighting/6133439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54593753</v>
+        <v>16071739</v>
       </c>
       <c r="B16" t="n">
-        <v>106230</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,21 +2278,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224098</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601121</v>
+        <v>601122</v>
       </c>
       <c r="R16" t="n">
-        <v>6276914</v>
+        <v>6276910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2340,12 +2335,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,16 +2351,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2375,16 +2375,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54593753</t>
+          <t>https://artportalen.se/Sighting/16071739</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6250674</v>
+        <v>60128607</v>
       </c>
       <c r="B17" t="n">
-        <v>104640</v>
+        <v>100797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,35 +2392,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224416</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
         <v>601191</v>
       </c>
       <c r="R17" t="n">
-        <v>6276888</v>
+        <v>6276883</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2447,12 +2449,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,18 +2468,18 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>f.d. banvall, kalkrik sand</t>
+          <t>Grusgrop, f d banvall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Bengt Hallberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2487,16 +2489,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6250674</t>
+          <t>https://artportalen.se/Sighting/60128607</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72696194</v>
+        <v>135288104</v>
       </c>
       <c r="B18" t="n">
-        <v>104640</v>
+        <v>100955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,37 +2506,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>222617</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601208</v>
+        <v>601301</v>
       </c>
       <c r="R18" t="n">
-        <v>6276952</v>
+        <v>6276866</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,12 +2560,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,32 +2574,359 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>torräng vid gammal skjutbana</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135288104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>54593753</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>601121</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6276914</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2015-07-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2015-07-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54593753</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6250674</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>601191</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6276888</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2009-10-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2009-10-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>f.d. banvall, kalkrik sand</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6250674</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>72696194</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dörbyskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>601208</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6276952</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>torräng vid gammal skjutbana</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/72696194</t>
         </is>
@@ -2622,6 +2951,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>104846</v>
+        <v>104848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>135288243</v>
       </c>
       <c r="B14" t="n">
-        <v>109984</v>
+        <v>109986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135288104</v>
       </c>
       <c r="B18" t="n">
-        <v>100955</v>
+        <v>100957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24778-2022 artfynd.xlsx
+++ b/artfynd/A 24778-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>135447260</v>
       </c>
       <c r="B9" t="n">
-        <v>104848</v>
+        <v>104868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
